--- a/docs/dq模板.xlsx
+++ b/docs/dq模板.xlsx
@@ -1,381 +1,181 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24980" windowHeight="11800" activeTab="3"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24980" windowHeight="11800" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="规则基本信息" sheetId="1" r:id="rId1"/>
-    <sheet name="参数配置" sheetId="2" r:id="rId2"/>
-    <sheet name="输出列配置" sheetId="3" r:id="rId3"/>
-    <sheet name="目录路径" sheetId="4" r:id="rId4"/>
-    <sheet name="备注(重要)" sheetId="5" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则基础信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数配置" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输出列配置" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目录路径" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="备注(重要)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="59">
-  <si>
-    <t>规则Number</t>
-  </si>
-  <si>
-    <t>规则ID</t>
-  </si>
-  <si>
-    <t>操作类型</t>
-  </si>
-  <si>
-    <t>规则中文名</t>
-  </si>
-  <si>
-    <t>规则英文名</t>
-  </si>
-  <si>
-    <t>规则中文描述</t>
-  </si>
-  <si>
-    <t>规则英文描述</t>
-  </si>
-  <si>
-    <t>检查范围</t>
-  </si>
-  <si>
-    <t>检查类型</t>
-  </si>
-  <si>
-    <t>配置方式</t>
-  </si>
-  <si>
-    <t>数据源</t>
-  </si>
-  <si>
-    <t>规则主题</t>
-  </si>
-  <si>
-    <t>规则分类</t>
-  </si>
-  <si>
-    <t>规则子分类</t>
-  </si>
-  <si>
-    <t>产品分类</t>
-  </si>
-  <si>
-    <t>产品子分类</t>
-  </si>
-  <si>
-    <t>数据质量特性</t>
-  </si>
-  <si>
-    <t>规则负责人</t>
-  </si>
-  <si>
-    <t>租户</t>
-  </si>
-  <si>
-    <t>目标表schema</t>
-  </si>
-  <si>
-    <t>目标表</t>
-  </si>
-  <si>
-    <t>目标表编码</t>
-  </si>
-  <si>
-    <t>参照表schema</t>
-  </si>
-  <si>
-    <t>参照表</t>
-  </si>
-  <si>
-    <t>参照表编码</t>
-  </si>
-  <si>
-    <t>参照表数据源</t>
-  </si>
-  <si>
-    <t>目标表环境变量</t>
-  </si>
-  <si>
-    <t>参照表环境变量</t>
-  </si>
-  <si>
-    <t>SQL</t>
-  </si>
-  <si>
-    <t>规则创建方式</t>
-  </si>
-  <si>
-    <t>ALLEntityCode</t>
-  </si>
-  <si>
-    <t>告警级别</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>序列号</t>
-  </si>
-  <si>
-    <t>参数名</t>
-  </si>
-  <si>
-    <t>默认值</t>
-  </si>
-  <si>
-    <t>参数业务含义</t>
-  </si>
-  <si>
-    <t>参数说明</t>
-  </si>
-  <si>
-    <t>维表编码</t>
-  </si>
-  <si>
-    <t>维表名</t>
-  </si>
-  <si>
-    <t>纬度属性编码</t>
-  </si>
-  <si>
-    <t>纬度属性名</t>
-  </si>
-  <si>
-    <t>纬度属性说明</t>
-  </si>
-  <si>
-    <t>数量</t>
-  </si>
-  <si>
-    <t>列原名</t>
-  </si>
-  <si>
-    <t>列索引名</t>
-  </si>
-  <si>
-    <t>列别名</t>
-  </si>
-  <si>
-    <t>维表字段名</t>
-  </si>
-  <si>
-    <t>权限控制纬度编码</t>
-  </si>
-  <si>
-    <t>权限控制纬度名</t>
-  </si>
-  <si>
-    <t>目标对象编码</t>
-  </si>
-  <si>
-    <t>目标对象属性编码</t>
-  </si>
-  <si>
-    <t>是否扩列</t>
-  </si>
-  <si>
-    <t>是否金额</t>
-  </si>
-  <si>
-    <t>是否默认显示</t>
-  </si>
-  <si>
-    <t>是否UCCID</t>
-  </si>
-  <si>
-    <t>金额列展示保留小数位数</t>
-  </si>
-  <si>
-    <t>列类型</t>
-  </si>
-  <si>
-    <t>目录路径</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -675,156 +475,156 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1072,7 +872,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1081,7 +881,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1094,11 +894,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1350,269 +1213,413 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AF1"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" spans="1:32">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>31</v>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>规则Number</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>规则ID</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>操作类型</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>规则中文名</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>规则英文名</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>规则中文描述</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>规则英文描述</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>检查范围</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>配置方式</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
+          <t>数据源</t>
+        </is>
+      </c>
+      <c r="L1" s="0" t="inlineStr">
+        <is>
+          <t>规则主题</t>
+        </is>
+      </c>
+      <c r="M1" s="0" t="inlineStr">
+        <is>
+          <t>规则分类</t>
+        </is>
+      </c>
+      <c r="N1" s="0" t="inlineStr">
+        <is>
+          <t>规则子分类</t>
+        </is>
+      </c>
+      <c r="O1" s="0" t="inlineStr">
+        <is>
+          <t>产品分类</t>
+        </is>
+      </c>
+      <c r="P1" s="0" t="inlineStr">
+        <is>
+          <t>产品子分类</t>
+        </is>
+      </c>
+      <c r="Q1" s="0" t="inlineStr">
+        <is>
+          <t>数据质量特性</t>
+        </is>
+      </c>
+      <c r="R1" s="0" t="inlineStr">
+        <is>
+          <t>规则负责人</t>
+        </is>
+      </c>
+      <c r="S1" s="0" t="inlineStr">
+        <is>
+          <t>租户</t>
+        </is>
+      </c>
+      <c r="T1" s="0" t="inlineStr">
+        <is>
+          <t>目标表schema</t>
+        </is>
+      </c>
+      <c r="U1" s="0" t="inlineStr">
+        <is>
+          <t>目标表</t>
+        </is>
+      </c>
+      <c r="V1" s="0" t="inlineStr">
+        <is>
+          <t>目标表编码</t>
+        </is>
+      </c>
+      <c r="W1" s="0" t="inlineStr">
+        <is>
+          <t>参照表schema</t>
+        </is>
+      </c>
+      <c r="X1" s="0" t="inlineStr">
+        <is>
+          <t>参照表</t>
+        </is>
+      </c>
+      <c r="Y1" s="0" t="inlineStr">
+        <is>
+          <t>参照表编码</t>
+        </is>
+      </c>
+      <c r="Z1" s="0" t="inlineStr">
+        <is>
+          <t>参照表数据源</t>
+        </is>
+      </c>
+      <c r="AA1" s="0" t="inlineStr">
+        <is>
+          <t>目标表环境变量</t>
+        </is>
+      </c>
+      <c r="AB1" s="0" t="inlineStr">
+        <is>
+          <t>参照表环境变量</t>
+        </is>
+      </c>
+      <c r="AC1" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="AD1" s="0" t="inlineStr">
+        <is>
+          <t>规则创建方式</t>
+        </is>
+      </c>
+      <c r="AE1" s="0" t="inlineStr">
+        <is>
+          <t>ALLEntityCode</t>
+        </is>
+      </c>
+      <c r="AF1" s="0" t="inlineStr">
+        <is>
+          <t>告警级别</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M1" t="s">
-        <v>43</v>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>规则ID</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>序列号</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>参数名</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>默认值</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>参数业务含义</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>参数说明</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>维表编码</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>维表名</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>纬度属性编码</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
+          <t>纬度属性名</t>
+        </is>
+      </c>
+      <c r="L1" s="0" t="inlineStr">
+        <is>
+          <t>纬度属性说明</t>
+        </is>
+      </c>
+      <c r="M1" s="0" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U1"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L1" t="s">
-        <v>49</v>
-      </c>
-      <c r="M1" t="s">
-        <v>50</v>
-      </c>
-      <c r="N1" t="s">
-        <v>51</v>
-      </c>
-      <c r="O1" t="s">
-        <v>52</v>
-      </c>
-      <c r="P1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>54</v>
-      </c>
-      <c r="R1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S1" t="s">
-        <v>56</v>
-      </c>
-      <c r="T1" t="s">
-        <v>43</v>
-      </c>
-      <c r="U1" t="s">
-        <v>57</v>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>规则ID</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>序列号</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>列原名</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>列索引名</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>列别名</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>维表编码</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>维表名</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>维表字段名</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
+          <t>权限控制纬度编码</t>
+        </is>
+      </c>
+      <c r="L1" s="0" t="inlineStr">
+        <is>
+          <t>权限控制纬度名</t>
+        </is>
+      </c>
+      <c r="M1" s="0" t="inlineStr">
+        <is>
+          <t>目标对象编码</t>
+        </is>
+      </c>
+      <c r="N1" s="0" t="inlineStr">
+        <is>
+          <t>目标对象属性编码</t>
+        </is>
+      </c>
+      <c r="O1" s="0" t="inlineStr">
+        <is>
+          <t>是否扩列</t>
+        </is>
+      </c>
+      <c r="P1" s="0" t="inlineStr">
+        <is>
+          <t>是否金额</t>
+        </is>
+      </c>
+      <c r="Q1" s="0" t="inlineStr">
+        <is>
+          <t>是否默认显示</t>
+        </is>
+      </c>
+      <c r="R1" s="0" t="inlineStr">
+        <is>
+          <t>是否UCCID</t>
+        </is>
+      </c>
+      <c r="S1" s="0" t="inlineStr">
+        <is>
+          <t>金额列展示保留小数位数</t>
+        </is>
+      </c>
+      <c r="T1" s="0" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="U1" s="0" t="inlineStr">
+        <is>
+          <t>列类型</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>58</v>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>规则ID</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>目录路径</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>